--- a/examples/emissions_poisoned.xlsx
+++ b/examples/emissions_poisoned.xlsx
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="B54" s="24" t="n">
-        <v>108.1</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55">
